--- a/laporan_padel_dki_jakarta_2026-10-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-21.xlsx
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.256.000</t>
+          <t>Rp1.344.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp438.000</t>
+          <t>Rp738.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.730.000</t>
+          <t>Rp2.612.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp100.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp6.120.000</t>
+          <t>Rp6.170.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp7.015.000</t>
+          <t>Rp7.140.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.815.500</t>
+          <t>Rp12.345.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.140.000</t>
+          <t>Rp5.290.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp15.200.000</t>
+          <t>Rp15.650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.193.000</t>
+          <t>Rp2.393.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.041.000</t>
+          <t>Rp3.938.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.924.000</t>
+          <t>Rp3.324.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp7.850.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.184.000</t>
+          <t>Rp6.034.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp37.450.000</t>
+          <t>Rp37.950.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.055.000</t>
+          <t>Rp1.770.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.475.000</t>
+          <t>Rp9.875.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.128.000</t>
+          <t>Rp6.959.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7486,21 +7486,21 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.775.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rp90.000 - Rp175.000</t>
+          <t>Rp70.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7548,16 +7548,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp8.705.000</t>
+          <t>Rp9.195.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.420.000</t>
+          <t>Rp7.020.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.974.992</t>
+          <t>Rp3.224.992</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.287.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.324.000</t>
+          <t>Rp3.436.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.730.000</t>
+          <t>Rp5.910.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-21.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.650.000</t>
+          <t>Rp15.390.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.344.000</t>
+          <t>Rp1.074.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp6.720.000</t>
+          <t>Rp7.520.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>67</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.382.985</t>
+          <t>Rp5.632.985</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.260.000</t>
+          <t>Rp9.260.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.368.000</t>
+          <t>Rp4.920.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.775.000</t>
+          <t>Rp3.875.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.995.000</t>
+          <t>Rp13.495.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.125.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp725.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.735.000</t>
+          <t>Rp6.115.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.886.000</t>
+          <t>Rp5.586.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.920.000</t>
+          <t>Rp3.120.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>56</v>
       </c>
       <c r="D50" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.608.000</t>
+          <t>Rp4.896.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp10.260.000</t>
+          <t>Rp11.020.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.840.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp70.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.320.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.484.000</t>
+          <t>Rp2.583.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>102</v>
       </c>
       <c r="D85" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp1.146.000</t>
+          <t>Rp1.345.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp6.675.000</t>
+          <t>Rp7.125.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>90</v>
       </c>
       <c r="D93" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp694.000</t>
+          <t>Rp934.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.080.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.345.500</t>
+          <t>Rp12.654.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.734.000</t>
+          <t>Rp5.834.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.360.000</t>
+          <t>Rp1.660.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp624.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp180.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rp90.000 - Rp125.000</t>
+          <t>Rp90.000</t>
         </is>
       </c>
     </row>
@@ -3974,16 +3974,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.299.000</t>
+          <t>Rp2.399.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp15.650.000</t>
+          <t>Rp16.550.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.393.000</t>
+          <t>Rp3.440.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp10.650.000</t>
+          <t>Rp11.000.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp16.845.000</t>
+          <t>Rp17.120.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.099.000</t>
+          <t>Rp1.549.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.575.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rp169.000 - Rp189.000</t>
+          <t>Rp99.000 - Rp179.000</t>
         </is>
       </c>
     </row>
@@ -4718,16 +4718,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp15.600.000</t>
+          <t>Rp15.900.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.275.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp71.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp6.325.000</t>
+          <t>Rp5.375.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.034.000</t>
+          <t>Rp6.144.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.625.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.260.000</t>
+          <t>Rp5.980.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.634.000</t>
+          <t>Rp1.994.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.270.000</t>
+          <t>Rp8.610.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6443,16 +6443,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp228.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.310.000</t>
+          <t>Rp9.590.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp69.000</t>
+          <t>Rp138.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp11.275.000</t>
+          <t>Rp11.975.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6773,21 +6773,21 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.612.000</t>
+          <t>Rp9.278.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp259.000</t>
+          <t>Rp99.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp18.413.500</t>
+          <t>Rp18.743.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.664.000</t>
+          <t>Rp4.852.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.287.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.700.000</t>
+          <t>Rp20.500.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.875.000</t>
+          <t>Rp11.850.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7207,21 +7207,21 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.959.000</t>
+          <t>Rp7.040.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp81.000 - Rp175.000</t>
+          <t>Rp10.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7238,16 +7238,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.540.000</t>
+          <t>Rp6.795.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp259.000</t>
+          <t>Rp659.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.165.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.075.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.610.000</t>
+          <t>Rp3.895.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp9.195.000</t>
+          <t>Rp9.440.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.325.000</t>
+          <t>Rp13.475.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.092.000</t>
+          <t>Rp2.280.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp23.675.000</t>
+          <t>Rp23.900.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.960.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp31.900.000</t>
+          <t>Rp32.400.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.790.000</t>
+          <t>Rp6.640.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.625.000</t>
+          <t>Rp7.925.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.540.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.020.000</t>
+          <t>Rp7.320.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.150.000</t>
+          <t>Rp7.850.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.012.000</t>
+          <t>Rp4.362.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.420.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>108</v>
       </c>
       <c r="D10" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.520.000</t>
+          <t>Rp2.180.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp24.200.000</t>
+          <t>Rp22.940.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.835.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.610.000</t>
+          <t>Rp2.180.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp1.765.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.975.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.736.000</t>
+          <t>Rp2.986.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>120</v>
       </c>
       <c r="D35" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.256.000</t>
+          <t>Rp4.654.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.310.000</t>
+          <t>Rp3.160.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>90</v>
       </c>
       <c r="D40" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp638.000</t>
+          <t>Rp1.434.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-21.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.060.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.488.000</t>
+          <t>Rp1.788.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp921.000</t>
+          <t>Rp125.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.632.985</t>
+          <t>Rp5.533.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.480.500</t>
+          <t>Rp10.608.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.875.000</t>
+          <t>Rp4.085.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp725.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,21 +1381,21 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.204.000</t>
+          <t>Rp1.544.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp200.000</t>
+          <t>Rp70.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.449.000</t>
+          <t>Rp1.647.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.612.000</t>
+          <t>Rp2.956.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.115.000</t>
+          <t>Rp5.355.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.896.000</t>
+          <t>Rp5.184.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>30</v>
       </c>
       <c r="D52" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp710.000</t>
+          <t>Rp1.090.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp96.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.530.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.172.000</t>
+          <t>Rp5.970.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>41</v>
       </c>
       <c r="D67" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.220.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.465.000</t>
+          <t>Rp2.593.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.505.500</t>
+          <t>Rp5.693.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp980.000</t>
+          <t>Rp1.565.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp6.170.000</t>
+          <t>Rp6.415.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.667.000</t>
+          <t>Rp5.363.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>135</v>
       </c>
       <c r="D84" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.030.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.840.000</t>
+          <t>Rp3.442.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp240.000</t>
+          <t>Rp150.700 - Rp200.200</t>
         </is>
       </c>
     </row>
@@ -3272,16 +3272,16 @@
         <v>28</v>
       </c>
       <c r="D92" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp2.615.000</t>
+          <t>Rp3.015.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp5.834.000</t>
+          <t>Rp8.168.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.290.000</t>
+          <t>Rp5.640.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp624.000</t>
+          <t>Rp799.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp180.000</t>
+          <t>Rp270.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp4.210.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp16.550.000</t>
+          <t>Rp16.100.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.375.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp11.000.000</t>
+          <t>Rp11.600.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp770.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.938.000</t>
+          <t>Rp3.589.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp17.120.000</t>
+          <t>Rp17.395.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.575.000</t>
+          <t>Rp6.925.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp385.000</t>
+          <t>Rp585.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.324.000</t>
+          <t>Rp2.660.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.675.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp71.000</t>
+          <t>Rp177.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp5.375.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp9.700.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.526.000</t>
+          <t>Rp6.120.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.144.000</t>
+          <t>Rp6.444.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp7.450.000</t>
+          <t>Rp8.450.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp25.960.000</t>
+          <t>Rp26.180.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.380.000</t>
+          <t>Rp1.780.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp37.950.000</t>
+          <t>Rp39.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.980.000</t>
+          <t>Rp6.160.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.994.000</t>
+          <t>Rp2.174.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.340.000</t>
+          <t>Rp12.420.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.590.000</t>
+          <t>Rp10.190.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp138.000</t>
+          <t>Rp536.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp12.890.000</t>
+          <t>Rp13.280.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp18.743.500</t>
+          <t>Rp19.583.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.852.000</t>
+          <t>Rp5.131.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.875.000</t>
+          <t>Rp10.125.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp6.194.000</t>
+          <t>Rp4.580.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.500.000</t>
+          <t>Rp20.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp11.850.000</t>
+          <t>Rp11.500.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.040.000</t>
+          <t>Rp7.390.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp6.950.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>84</v>
       </c>
       <c r="D30" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.070.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.075.000</t>
+          <t>Rp2.775.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp9.440.000</t>
+          <t>Rp9.195.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.475.000</t>
+          <t>Rp14.575.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp2.280.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp3.144.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp23.900.000</t>
+          <t>Rp24.250.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.910.000</t>
+          <t>Rp6.710.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp9.837.000</t>
+          <t>Rp10.535.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.640.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.925.000</t>
+          <t>Rp8.950.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.320.000</t>
+          <t>Rp7.605.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.362.000</t>
+          <t>Rp3.465.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.420.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp22.940.000</t>
+          <t>Rp23.420.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp320.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp4.635.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.910.000</t>
+          <t>Rp5.130.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.374.990</t>
+          <t>Rp4.574.989</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp3.455.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.079.000</t>
+          <t>Rp2.376.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp1.660.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-21.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp15.390.000</t>
+          <t>Rp15.690.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.788.000</t>
+          <t>Rp2.088.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.625.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.544.000</t>
+          <t>Rp2.144.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp96.000</t>
+          <t>Rp192.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.693.000</t>
+          <t>Rp5.943.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.565.000</t>
+          <t>Rp1.905.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>102</v>
       </c>
       <c r="D85" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp7.125.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.015.000</t>
+          <t>Rp3.265.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp11.600.000</t>
+          <t>Rp11.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp770.000</t>
+          <t>Rp1.540.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.120.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.695.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.420.000</t>
+          <t>Rp13.040.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp11.975.000</t>
+          <t>Rp12.325.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp2.820.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.580.000</t>
+          <t>Rp5.118.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.200.000</t>
+          <t>Rp20.600.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.795.000</t>
+          <t>Rp6.945.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.950.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp9.195.000</t>
+          <t>Rp9.685.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp14.575.000</t>
+          <t>Rp14.625.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.144.000</t>
+          <t>Rp2.856.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp8.000.000</t>
+          <t>Rp8.680.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.465.000</t>
+          <t>Rp4.063.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.425.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.986.000</t>
+          <t>Rp3.631.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.455.000</t>
+          <t>Rp3.975.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.376.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.434.000</t>
+          <t>Rp1.832.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.608.500</t>
+          <t>Rp10.686.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.085.000</t>
+          <t>Rp4.185.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.355.000</t>
+          <t>Rp5.480.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1777,28 +1777,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Level 9 Padel</t>
+          <t>Playfieldcourt - Palmerah</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>198</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>173</v>
+        <v>2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp150.000</t>
+          <t>Rp100.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -1808,28 +1808,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Como Padel Court</t>
+          <t>The Level 9 Padel</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>60</v>
+        <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp210.000</t>
+          <t>Rp125.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -1839,28 +1839,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>World Padel</t>
+          <t>Como Padel Court</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D46" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp225.000</t>
+          <t>Rp99.000 - Rp210.000</t>
         </is>
       </c>
     </row>
@@ -1870,28 +1870,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Padelin</t>
+          <t>World Padel</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D47" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp3.120.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp200.000</t>
+          <t>Rp50.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -1901,28 +1901,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Courtyard Padel Club</t>
+          <t>Padelin</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="D48" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp3.220.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp600.000</t>
+          <t>Rp70.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1932,28 +1932,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Padel On Mars</t>
+          <t>Courtyard Padel Club</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp270.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rp115.000 - Rp135.000</t>
+          <t>Rp100.000 - Rp600.000</t>
         </is>
       </c>
     </row>
@@ -1963,28 +1963,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Padel Meruya Airdome</t>
+          <t>Padel On Mars</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D50" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp270.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp275.000 - Rp550.000</t>
+          <t>Rp115.000 - Rp135.000</t>
         </is>
       </c>
     </row>
@@ -1994,28 +1994,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hachi Padel Puri Indah Jakarta</t>
+          <t>Padel Meruya Airdome</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.184.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rp288.000</t>
+          <t>Rp275.000 - Rp550.000</t>
         </is>
       </c>
     </row>
@@ -2025,28 +2025,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JC Padel Kedoya</t>
+          <t>Hachi Padel Puri Indah Jakarta</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.090.000</t>
+          <t>Rp5.184.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp380.000</t>
+          <t>Rp288.000</t>
         </is>
       </c>
     </row>
@@ -2056,28 +2056,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tennis Padel Matic Mal Ciputra</t>
+          <t>JC Padel Kedoya</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp192.000</t>
+          <t>Rp1.090.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rp96.000 - Rp120.000</t>
+          <t>Rp100.000 - Rp380.000</t>
         </is>
       </c>
     </row>
@@ -2087,28 +2087,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Paddle Padel</t>
+          <t>Tennis Padel Matic Mal Ciputra</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp192.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp175.000</t>
+          <t>Rp96.000 - Rp120.000</t>
         </is>
       </c>
     </row>
@@ -2118,28 +2118,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Roots Padel House</t>
+          <t>Paddle Padel</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rp149.000 - Rp200.000</t>
+          <t>Rp150.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -2149,28 +2149,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Coco Padel Court Jakarta</t>
+          <t>Roots Padel House</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp180.000</t>
+          <t>Rp149.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2180,28 +2180,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zplay Padel</t>
+          <t>Coco Padel Court Jakarta</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.535.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rp65.000 - Rp145.000</t>
+          <t>Rp100.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -2211,28 +2211,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PPC - Puri Padel Club</t>
+          <t>Zplay Padel</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp3.125.000</t>
+          <t>Rp1.535.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rp225.000 - Rp275.000</t>
+          <t>Rp65.000 - Rp145.000</t>
         </is>
       </c>
     </row>
@@ -2242,28 +2242,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Donkey Padel</t>
+          <t>PPC - Puri Padel Club</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp745.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp149.000</t>
+          <t>Rp225.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -2273,28 +2273,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sunrise Padel - Sunrise Garden</t>
+          <t>Donkey Padel</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp100.000</t>
+          <t>Rp745.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp199.000</t>
+          <t>Rp99.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -2304,28 +2304,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ace Padel Club (APC) - Jalan Panjang Kedoya</t>
+          <t>Sunrise Padel - Sunrise Garden</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp11.020.000</t>
+          <t>Rp100.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp300.000</t>
+          <t>Rp75.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -2335,28 +2335,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Padel Quarter</t>
+          <t>Ace Padel Club (APC) - Jalan Panjang Kedoya</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp3.530.000</t>
+          <t>Rp11.020.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp380.000</t>
+          <t>Rp100.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -2366,28 +2366,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZEN PADEL</t>
+          <t>Padel Quarter</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp3.530.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp99.000</t>
+          <t>Rp75.000 - Rp380.000</t>
         </is>
       </c>
     </row>
@@ -2397,28 +2397,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Go 2 Padel</t>
+          <t>ZEN PADEL</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D64" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rp60.000 - Rp150.000</t>
+          <t>Rp70.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -2428,28 +2428,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YOLO Padel and Lifestyle Slipi</t>
+          <t>Go 2 Padel</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp375.000</t>
+          <t>Rp60.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -2459,28 +2459,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KALMA Social Club - Jl. Panjang, Kedoya</t>
+          <t>YOLO Padel and Lifestyle Slipi</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="D66" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.970.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp399.000</t>
+          <t>Rp300.000 - Rp375.000</t>
         </is>
       </c>
     </row>
@@ -2490,28 +2490,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Padel V</t>
+          <t>KALMA Social Club - Jl. Panjang, Kedoya</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.220.000</t>
+          <t>Rp5.970.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp260.000</t>
+          <t>Rp150.000 - Rp399.000</t>
         </is>
       </c>
     </row>
@@ -2521,28 +2521,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Country Club | Padel &amp; Lounge</t>
+          <t>Padel V</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>41</v>
+      </c>
+      <c r="D68" t="n">
         <v>34</v>
       </c>
-      <c r="D68" t="n">
-        <v>15</v>
-      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.593.000</t>
+          <t>Rp1.220.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp188.000</t>
+          <t>Rp70.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -2552,28 +2552,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Social Field</t>
+          <t>Country Club | Padel &amp; Lounge</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>176</v>
+        <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.590.000</t>
+          <t>Rp2.593.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rp99.500 - Rp299.000</t>
+          <t>Rp99.000 - Rp188.000</t>
         </is>
       </c>
     </row>
@@ -2583,28 +2583,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PIPC - Play In Padel Collective - Srengseng</t>
+          <t>Social Field</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.943.000</t>
+          <t>Rp2.590.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp250.000</t>
+          <t>Rp99.500 - Rp299.000</t>
         </is>
       </c>
     </row>
@@ -2614,28 +2614,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>United Padel Club</t>
+          <t>PIPC - Play In Padel Collective - Srengseng</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp5.943.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rp120.000 - Rp180.000</t>
+          <t>Rp99.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -2645,28 +2645,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Powerhouse Padel AZURE Taman Surya</t>
+          <t>United Padel Club</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.905.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp170.000</t>
+          <t>Rp120.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -2676,28 +2676,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kore Padel</t>
+          <t>Powerhouse Padel AZURE Taman Surya</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp2.055.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp325.000</t>
+          <t>Rp75.000 - Rp170.000</t>
         </is>
       </c>
     </row>
@@ -2707,28 +2707,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OLA PADEL CLUB</t>
+          <t>Kore Padel</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp2.620.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp260.000</t>
+          <t>Rp200.000 - Rp325.000</t>
         </is>
       </c>
     </row>
@@ -2738,28 +2738,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MMT Padel</t>
+          <t>OLA PADEL CLUB</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp2.620.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp315.000</t>
+          <t>Rp100.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -2769,28 +2769,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Padel En Pilar</t>
+          <t>MMT Padel</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp150.000 - Rp315.000</t>
         </is>
       </c>
     </row>
@@ -2800,28 +2800,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Clubhouse Meruya</t>
+          <t>Padel En Pilar</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp6.415.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp245.000</t>
+          <t>Rp150.000</t>
         </is>
       </c>
     </row>
@@ -2831,28 +2831,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Angke Padel</t>
+          <t>Clubhouse Meruya</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp6.415.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp150.000</t>
+          <t>Rp100.000 - Rp245.000</t>
         </is>
       </c>
     </row>
@@ -2862,28 +2862,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DAAN MOGOT PADEL COURT</t>
+          <t>Angke Padel</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp500.000</t>
+          <t>Rp50.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -2893,28 +2893,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kaia Padel Reserve</t>
+          <t>DAAN MOGOT PADEL COURT</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp5.363.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp199.000</t>
+          <t>Rp50.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -2924,28 +2924,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tangkas Padel</t>
+          <t>Kaia Padel Reserve</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.583.000</t>
+          <t>Rp5.561.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp199.000</t>
+          <t>Rp50.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -2955,28 +2955,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cosmo Padel</t>
+          <t>Tangkas Padel</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp2.583.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp275.000</t>
+          <t>Rp99.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -2986,28 +2986,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MAISON de PADEL</t>
+          <t>Cosmo Padel</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rp275.000 - Rp450.000</t>
+          <t>Rp100.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Di Atas Social Club - Lippo Mall Puri</t>
+          <t>MAISON de PADEL</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="D84" t="n">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp4.030.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rp195.000 - Rp280.000</t>
+          <t>Rp275.000 - Rp450.000</t>
         </is>
       </c>
     </row>
@@ -3048,28 +3048,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Commune Courts</t>
+          <t>Di Atas Social Club - Lippo Mall Puri</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp4.030.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp300.000</t>
+          <t>Rp195.000 - Rp280.000</t>
         </is>
       </c>
     </row>
@@ -3079,28 +3079,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EL WILLY PADEL</t>
+          <t>Commune Courts</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D86" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp250.000</t>
+          <t>Rp100.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -3110,28 +3110,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dash Padel House</t>
+          <t>EL WILLY PADEL</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp1.345.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp249.000</t>
+          <t>Rp200.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -3141,28 +3141,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Citra Padel Club</t>
+          <t>Dash Padel House</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp1.345.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp225.000</t>
+          <t>Rp100.000 - Rp249.000</t>
         </is>
       </c>
     </row>
@@ -3172,28 +3172,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Malta Padel Club</t>
+          <t>Citra Padel Club</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.442.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rp150.700 - Rp200.200</t>
+          <t>Rp70.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -3203,28 +3203,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>De Luz Padel</t>
+          <t>Malta Padel Club</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D90" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp7.140.000</t>
+          <t>Rp3.442.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp180.000</t>
+          <t>Rp150.700 - Rp200.200</t>
         </is>
       </c>
     </row>
@@ -3234,28 +3234,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dale Padel</t>
+          <t>De Luz Padel</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp7.140.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rp60.000 - Rp175.000</t>
+          <t>Rp80.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -3265,28 +3265,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nice Padel</t>
+          <t>Dale Padel</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp60.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -3296,28 +3296,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Golcindo Padel &amp; Mahjong</t>
+          <t>Nice Padel</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp934.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp149.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
     </row>
@@ -3327,28 +3327,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mono House</t>
+          <t>Golcindo Padel &amp; Mahjong</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="D94" t="n">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp934.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp225.000</t>
+          <t>Rp50.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -3358,28 +3358,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Elite Padel Club - Puri</t>
+          <t>Mono House</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp4.974.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rp149.000 - Rp249.000</t>
+          <t>Rp125.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -3389,28 +3389,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Seven Stars Arena</t>
+          <t>Elite Padel Club - Puri</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp4.974.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp220.000</t>
+          <t>Rp149.000 - Rp249.000</t>
         </is>
       </c>
     </row>
@@ -3420,28 +3420,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deuce Arena</t>
+          <t>Seven Stars Arena</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.265.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp250.000</t>
+          <t>Rp75.000 - Rp220.000</t>
         </is>
       </c>
     </row>
@@ -3451,28 +3451,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Alley Social Padel Mahjong By Homeground</t>
+          <t>Deuce Arena</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.546.000</t>
+          <t>Rp3.265.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp199.000</t>
+          <t>Rp80.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -3482,28 +3482,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Athena Arena</t>
+          <t>Alley Social Padel Mahjong By Homeground</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D99" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.546.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp200.000</t>
+          <t>Rp50.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -3513,28 +3513,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SERA COMMUNITY CLUB</t>
+          <t>Athena Arena</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D100" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rp1.530.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rp165.000 - Rp400.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -3544,26 +3544,57 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>SERA COMMUNITY CLUB</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>28</v>
+      </c>
+      <c r="D101" t="n">
+        <v>23</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>17.9%</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Rp1.530.000</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Rp165.000 - Rp400.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>Playfieldcourt Padel Srengseng</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C102" t="n">
         <v>36</v>
       </c>
-      <c r="D101" t="n">
-        <v>18</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Rp2.700.000</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
+      <c r="D102" t="n">
+        <v>16</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Rp3.000.000</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>Rp150.000</t>
         </is>
@@ -3726,16 +3757,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4129,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.375.000</t>
+          <t>Rp5.575.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4346,16 +4377,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.540.000</t>
+          <t>Rp1.815.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4966,16 +4997,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp1.295.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5183,16 +5214,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.850.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5648,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.444.000</t>
+          <t>Rp6.594.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6009,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6587,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.040.000</t>
+          <t>Rp13.740.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6587,16 +6618,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.300.000</t>
+          <t>Rp7.550.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6649,16 +6680,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp536.000</t>
+          <t>Rp734.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6835,16 +6866,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp19.583.500</t>
+          <t>Rp19.820.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7145,16 +7176,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.600.000</t>
+          <t>Rp20.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7579,16 +7610,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp14.625.000</t>
+          <t>Rp14.900.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7610,16 +7641,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.732.000</t>
+          <t>Rp3.920.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7641,16 +7672,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.479.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7827,16 +7858,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8498,16 +8529,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp8.125.000</t>
+          <t>Rp8.325.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8932,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.574.989</t>
+          <t>Rp4.324.989</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9211,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9304,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.673.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
